--- a/exports/trend_1d/WIPRO_full_report.xlsx
+++ b/exports/trend_1d/WIPRO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42089</v>
+        <v>42090</v>
       </c>
       <c r="H2" t="n">
-        <v>113.55</v>
+        <v>109.95</v>
       </c>
       <c r="I2" t="n">
         <v>112.490163154167</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>12.99</v>
+        <v>9.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.94</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42206</v>
+        <v>42207</v>
       </c>
       <c r="H3" t="n">
-        <v>103.6</v>
+        <v>105.05</v>
       </c>
       <c r="I3" t="n">
         <v>103.9169571146865</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K3" t="n">
-        <v>5.78</v>
+        <v>4.46</v>
       </c>
       <c r="L3" t="n">
         <v>4.82</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.92</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H4" t="n">
-        <v>97.8</v>
+        <v>97.25</v>
       </c>
       <c r="I4" t="n">
         <v>97.77530624470509</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.9</v>
+        <v>-7.43</v>
       </c>
       <c r="L4" t="n">
-        <v>8.33</v>
+        <v>9.66</v>
       </c>
       <c r="M4" t="n">
         <v>1.26</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42263</v>
+        <v>42265</v>
       </c>
       <c r="H5" t="n">
-        <v>104.25</v>
+        <v>106.4</v>
       </c>
       <c r="I5" t="n">
         <v>106.1030412503626</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.2</v>
+        <v>-9.41</v>
       </c>
       <c r="L5" t="n">
-        <v>7.51</v>
+        <v>9.92</v>
       </c>
       <c r="M5" t="n">
         <v>1.16</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.97</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>102.4</v>
+        <v>100.65</v>
       </c>
       <c r="I6" t="n">
         <v>101.2200108813137</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.76</v>
+        <v>-5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>4.61</v>
+        <v>6.11</v>
       </c>
       <c r="M6" t="n">
         <v>1.22</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>5.71</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42338</v>
+        <v>42339</v>
       </c>
       <c r="H7" t="n">
-        <v>103</v>
+        <v>104.55</v>
       </c>
       <c r="I7" t="n">
         <v>104.2311855649295</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.33</v>
+        <v>-3.87</v>
       </c>
       <c r="L7" t="n">
-        <v>3.08</v>
+        <v>4.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
         <v>2.35</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.18</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>99.75</v>
+        <v>98.8</v>
       </c>
       <c r="I8" t="n">
         <v>99.13417912379674</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.59</v>
+        <v>-5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>5.74</v>
+        <v>5.98</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.97</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42458</v>
+        <v>42459</v>
       </c>
       <c r="H9" t="n">
-        <v>99.40000000000001</v>
+        <v>101</v>
       </c>
       <c r="I9" t="n">
         <v>100.4440972828847</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.61</v>
+        <v>-2.23</v>
       </c>
       <c r="L9" t="n">
         <v>4.4</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.19</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42482</v>
+        <v>42485</v>
       </c>
       <c r="H10" t="n">
-        <v>100.25</v>
+        <v>99.3</v>
       </c>
       <c r="I10" t="n">
         <v>100.0548704876353</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.74</v>
+        <v>-1.68</v>
       </c>
       <c r="L10" t="n">
         <v>3.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.06</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42542</v>
+        <v>42543</v>
       </c>
       <c r="H11" t="n">
-        <v>100.8</v>
+        <v>101.2</v>
       </c>
       <c r="I11" t="n">
         <v>100.8159885305134</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.51</v>
+        <v>-1.91</v>
       </c>
       <c r="L11" t="n">
         <v>2.06</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>4.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42570</v>
+        <v>42571</v>
       </c>
       <c r="H12" t="n">
-        <v>98.7</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>98.39656314442608</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.47</v>
+        <v>-4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>1.88</v>
+        <v>5.72</v>
       </c>
       <c r="N12" t="n">
         <v>2.78</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>4.97</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42661</v>
+        <v>42662</v>
       </c>
       <c r="H13" t="n">
-        <v>86.75</v>
+        <v>88.95</v>
       </c>
       <c r="I13" t="n">
         <v>88.24737835317555</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K13" t="n">
-        <v>10.43</v>
+        <v>8.16</v>
       </c>
       <c r="L13" t="n">
         <v>4.23</v>
@@ -1182,7 +1337,7 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="O13" t="n">
         <v>-1.87</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.34</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42668</v>
+        <v>42669</v>
       </c>
       <c r="H14" t="n">
-        <v>86.5</v>
+        <v>84.7</v>
       </c>
       <c r="I14" t="n">
         <v>85.26231256248151</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.75</v>
+        <v>-4.78</v>
       </c>
       <c r="L14" t="n">
-        <v>3.49</v>
+        <v>4.95</v>
       </c>
       <c r="M14" t="n">
         <v>1.84</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>6.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42704</v>
+        <v>42705</v>
       </c>
       <c r="H15" t="n">
-        <v>83.59999999999999</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>84.07278424632297</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3</v>
+        <v>0.65</v>
       </c>
       <c r="L15" t="n">
         <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="N15" t="n">
         <v>3.09</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.98</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42766</v>
+        <v>42767</v>
       </c>
       <c r="H16" t="n">
-        <v>82.3</v>
+        <v>81.95</v>
       </c>
       <c r="I16" t="n">
         <v>82.2605843421765</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2</v>
+        <v>-2.61</v>
       </c>
       <c r="L16" t="n">
         <v>4.93</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42788</v>
+        <v>42789</v>
       </c>
       <c r="H17" t="n">
-        <v>85.25</v>
+        <v>87.3</v>
       </c>
       <c r="I17" t="n">
         <v>86.90732799604162</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.03</v>
+        <v>-6.53</v>
       </c>
       <c r="L17" t="n">
-        <v>6.04</v>
+        <v>7.26</v>
       </c>
       <c r="M17" t="n">
         <v>0.61</v>
       </c>
       <c r="N17" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
         <v>-0.43</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.85</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42898</v>
+        <v>42899</v>
       </c>
       <c r="H18" t="n">
-        <v>94.55</v>
+        <v>93.05</v>
       </c>
       <c r="I18" t="n">
         <v>94.47016081626428</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K18" t="n">
-        <v>8.300000000000001</v>
+        <v>6.59</v>
       </c>
       <c r="L18" t="n">
         <v>2.98</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42936</v>
+        <v>42937</v>
       </c>
       <c r="H19" t="n">
-        <v>96.75</v>
+        <v>102.8</v>
       </c>
       <c r="I19" t="n">
         <v>98.14418901197848</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.98</v>
+        <v>-10.48</v>
       </c>
       <c r="L19" t="n">
-        <v>5.91</v>
+        <v>12.31</v>
       </c>
       <c r="M19" t="n">
-        <v>2.52</v>
+        <v>5.43</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>6.25</v>
       </c>
       <c r="O19" t="n">
         <v>-1.59</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42991</v>
+        <v>42992</v>
       </c>
       <c r="H20" t="n">
-        <v>106.35</v>
+        <v>101.8</v>
       </c>
       <c r="I20" t="n">
         <v>104.8499083019836</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>-0.97</v>
       </c>
       <c r="L20" t="n">
         <v>2.04</v>
       </c>
       <c r="M20" t="n">
-        <v>0.37</v>
+        <v>4.89</v>
       </c>
       <c r="N20" t="n">
-        <v>1.56</v>
+        <v>4.28</v>
       </c>
       <c r="O20" t="n">
         <v>6.25</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.65</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H21" t="n">
-        <v>106.7</v>
+        <v>107.4</v>
       </c>
       <c r="I21" t="n">
         <v>107.0394468546182</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.81</v>
+        <v>-5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>5.6</v>
+        <v>6.58</v>
       </c>
       <c r="M21" t="n">
         <v>1.33</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.17</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43073</v>
+        <v>43074</v>
       </c>
       <c r="H22" t="n">
-        <v>104.2</v>
+        <v>101.8</v>
       </c>
       <c r="I22" t="n">
         <v>103.2466872676295</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.98</v>
+        <v>-5.21</v>
       </c>
       <c r="L22" t="n">
         <v>5.35</v>
@@ -1695,7 +1958,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
         <v>0.66</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>6.82</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43090</v>
+        <v>43091</v>
       </c>
       <c r="H23" t="n">
-        <v>107</v>
+        <v>108.4</v>
       </c>
       <c r="I23" t="n">
         <v>107.2405957468697</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.11</v>
+        <v>-6.48</v>
       </c>
       <c r="L23" t="n">
-        <v>5.55</v>
+        <v>7.12</v>
       </c>
       <c r="M23" t="n">
         <v>0.86</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H24" t="n">
-        <v>109.45</v>
+        <v>108.05</v>
       </c>
       <c r="I24" t="n">
         <v>108.170983818221</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>0.97</v>
+        <v>-0.32</v>
       </c>
       <c r="L24" t="n">
         <v>1.85</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.24</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43291</v>
+        <v>43292</v>
       </c>
       <c r="H25" t="n">
-        <v>97.25</v>
+        <v>97.8</v>
       </c>
       <c r="I25" t="n">
         <v>97.56787791101316</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>9.49</v>
       </c>
       <c r="L25" t="n">
         <v>2.82</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.38</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43395</v>
+        <v>43396</v>
       </c>
       <c r="H26" t="n">
-        <v>115.8</v>
+        <v>111.1</v>
       </c>
       <c r="I26" t="n">
         <v>111.9172590732355</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K26" t="n">
-        <v>18.4</v>
+        <v>13.6</v>
       </c>
       <c r="L26" t="n">
         <v>3.27</v>
@@ -1923,7 +2234,7 @@
         <v>2.51</v>
       </c>
       <c r="N26" t="n">
-        <v>2.76</v>
+        <v>4.06</v>
       </c>
       <c r="O26" t="n">
         <v>0.57</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.63</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43438</v>
+        <v>43439</v>
       </c>
       <c r="H27" t="n">
-        <v>120.35</v>
+        <v>120.95</v>
       </c>
       <c r="I27" t="n">
         <v>120.6194684826914</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.33</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>10.4</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.34</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43530</v>
+        <v>43531</v>
       </c>
       <c r="H28" t="n">
-        <v>132.6</v>
+        <v>128.5</v>
       </c>
       <c r="I28" t="n">
         <v>129.6117054863977</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K28" t="n">
-        <v>9.630000000000001</v>
+        <v>6.24</v>
       </c>
       <c r="L28" t="n">
         <v>7.52</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>11.22</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43564</v>
+        <v>43565</v>
       </c>
       <c r="H29" t="n">
-        <v>130.85</v>
+        <v>134.3</v>
       </c>
       <c r="I29" t="n">
         <v>130.9649312932711</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.83</v>
+        <v>-4.51</v>
       </c>
       <c r="L29" t="n">
-        <v>4.24</v>
+        <v>4.79</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="N29" t="n">
         <v>3.81</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>7.98</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43635</v>
+        <v>43636</v>
       </c>
       <c r="H30" t="n">
-        <v>140.5</v>
+        <v>137.15</v>
       </c>
       <c r="I30" t="n">
         <v>137.8667869405126</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K30" t="n">
-        <v>4.62</v>
+        <v>2.12</v>
       </c>
       <c r="L30" t="n">
         <v>2.16</v>
       </c>
       <c r="M30" t="n">
-        <v>0.32</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O30" t="n">
         <v>2.64</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.47</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43756</v>
+        <v>43760</v>
       </c>
       <c r="H31" t="n">
-        <v>119</v>
+        <v>121.2</v>
       </c>
       <c r="I31" t="n">
         <v>120.6629728393631</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K31" t="n">
-        <v>13.23</v>
+        <v>11.63</v>
       </c>
       <c r="L31" t="n">
         <v>1.02</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>7.45</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43790</v>
+        <v>43791</v>
       </c>
       <c r="H32" t="n">
-        <v>118.35</v>
+        <v>116.2</v>
       </c>
       <c r="I32" t="n">
         <v>116.7284319285595</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.35</v>
+        <v>-4.13</v>
       </c>
       <c r="L32" t="n">
-        <v>2.6</v>
+        <v>4.54</v>
       </c>
       <c r="M32" t="n">
-        <v>0.42</v>
+        <v>1.73</v>
       </c>
       <c r="N32" t="n">
         <v>1.89</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.54</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43817</v>
+        <v>43818</v>
       </c>
       <c r="H33" t="n">
-        <v>118.7</v>
+        <v>119.1</v>
       </c>
       <c r="I33" t="n">
         <v>119.0912023947819</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.15</v>
+        <v>-2.5</v>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.74</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H34" t="n">
-        <v>117.95</v>
+        <v>115.05</v>
       </c>
       <c r="I34" t="n">
         <v>116.5240923504476</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.97</v>
+        <v>-3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>2.98</v>
+        <v>3.61</v>
       </c>
       <c r="M34" t="n">
         <v>1.26</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.12</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43977</v>
+        <v>43978</v>
       </c>
       <c r="H35" t="n">
-        <v>90.2</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>95.68691304961987</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K35" t="n">
-        <v>21.6</v>
+        <v>16.43</v>
       </c>
       <c r="L35" t="n">
         <v>3.3</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44130</v>
+        <v>44131</v>
       </c>
       <c r="H36" t="n">
-        <v>162.4</v>
+        <v>159.65</v>
       </c>
       <c r="I36" t="n">
         <v>162.0534446643012</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K36" t="n">
-        <v>68.90000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>6.71</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.16</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44187</v>
+        <v>44188</v>
       </c>
       <c r="H37" t="n">
-        <v>174.05</v>
+        <v>184.3</v>
       </c>
       <c r="I37" t="n">
         <v>174.1398051953483</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.02</v>
+        <v>-15.44</v>
       </c>
       <c r="L37" t="n">
-        <v>10.08</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>1.46</v>
+        <v>2.7</v>
       </c>
       <c r="N37" t="n">
-        <v>2.87</v>
+        <v>5.89</v>
       </c>
       <c r="O37" t="n">
         <v>-1.69</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.74</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H38" t="n">
-        <v>206.4</v>
+        <v>199.75</v>
       </c>
       <c r="I38" t="n">
         <v>201.1296656200086</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K38" t="n">
-        <v>11.99</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L38" t="n">
         <v>3.61</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.96</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44293</v>
+        <v>44294</v>
       </c>
       <c r="H39" t="n">
-        <v>209.35</v>
+        <v>211.3</v>
       </c>
       <c r="I39" t="n">
         <v>210.0070040876373</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.81</v>
+        <v>-5.78</v>
       </c>
       <c r="L39" t="n">
         <v>8.109999999999999</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.28</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44385</v>
+        <v>44386</v>
       </c>
       <c r="H40" t="n">
-        <v>253.8</v>
+        <v>251.3</v>
       </c>
       <c r="I40" t="n">
         <v>253.1542809115379</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K40" t="n">
-        <v>20.11</v>
+        <v>18.93</v>
       </c>
       <c r="L40" t="n">
         <v>6.67</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.88</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44390</v>
+        <v>44391</v>
       </c>
       <c r="H41" t="n">
-        <v>250.8</v>
+        <v>268.45</v>
       </c>
       <c r="I41" t="n">
         <v>265.0085712420065</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2</v>
+        <v>-6.82</v>
       </c>
       <c r="L41" t="n">
-        <v>1.21</v>
+        <v>7.12</v>
       </c>
       <c r="M41" t="n">
         <v>0.96</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="O41" t="n">
         <v>-0.99</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.69</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44466</v>
+        <v>44467</v>
       </c>
       <c r="H42" t="n">
-        <v>312.55</v>
+        <v>305.65</v>
       </c>
       <c r="I42" t="n">
         <v>308.1447306772493</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K42" t="n">
-        <v>16.43</v>
+        <v>13.86</v>
       </c>
       <c r="L42" t="n">
         <v>6.43</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.18</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44482</v>
+        <v>44483</v>
       </c>
       <c r="H43" t="n">
-        <v>321.45</v>
+        <v>338.45</v>
       </c>
       <c r="I43" t="n">
         <v>325.3514239823911</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.17</v>
+        <v>-10.73</v>
       </c>
       <c r="L43" t="n">
-        <v>5.5</v>
+        <v>15.67</v>
       </c>
       <c r="M43" t="n">
-        <v>0.89</v>
+        <v>3.62</v>
       </c>
       <c r="N43" t="n">
-        <v>2.83</v>
+        <v>5.29</v>
       </c>
       <c r="O43" t="n">
         <v>-2.21</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>8.24</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H44" t="n">
-        <v>313.95</v>
+        <v>309.1</v>
       </c>
       <c r="I44" t="n">
         <v>311.9343031467765</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.24</v>
+        <v>-8.67</v>
       </c>
       <c r="L44" t="n">
-        <v>7.52</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>0.02</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>10.22</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H45" t="n">
-        <v>307.9</v>
+        <v>320.55</v>
       </c>
       <c r="I45" t="n">
         <v>319.9753071469797</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K45" t="n">
-        <v>0.39</v>
+        <v>-3.7</v>
       </c>
       <c r="L45" t="n">
-        <v>3.41</v>
+        <v>4.64</v>
       </c>
       <c r="M45" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="N45" t="n">
-        <v>2.82</v>
+        <v>4.11</v>
       </c>
       <c r="O45" t="n">
         <v>-1.54</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.57</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H46" t="n">
-        <v>330.4</v>
+        <v>310.55</v>
       </c>
       <c r="I46" t="n">
         <v>324.4213452584837</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K46" t="n">
-        <v>3.07</v>
+        <v>-3.12</v>
       </c>
       <c r="L46" t="n">
-        <v>3.07</v>
+        <v>3.38</v>
       </c>
       <c r="M46" t="n">
-        <v>1.09</v>
+        <v>4.07</v>
       </c>
       <c r="N46" t="n">
-        <v>2.51</v>
+        <v>6.01</v>
       </c>
       <c r="O46" t="n">
         <v>4.11</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H47" t="n">
-        <v>280.15</v>
+        <v>285.85</v>
       </c>
       <c r="I47" t="n">
         <v>284.2815017021377</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K47" t="n">
-        <v>9.789999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="L47" t="n">
         <v>2.5</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.73</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44662</v>
+        <v>44663</v>
       </c>
       <c r="H48" t="n">
-        <v>272.95</v>
+        <v>267</v>
       </c>
       <c r="I48" t="n">
         <v>271.2316146629893</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.51</v>
+        <v>-6.59</v>
       </c>
       <c r="L48" t="n">
-        <v>5.02</v>
+        <v>7</v>
       </c>
       <c r="M48" t="n">
         <v>0.68</v>
       </c>
       <c r="N48" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
         <v>2.03</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.34</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H49" t="n">
-        <v>202.45</v>
+        <v>205</v>
       </c>
       <c r="I49" t="n">
         <v>204.8522859218978</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K49" t="n">
-        <v>24.18</v>
+        <v>23.22</v>
       </c>
       <c r="L49" t="n">
         <v>1.67</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.17</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44797</v>
+        <v>44798</v>
       </c>
       <c r="H50" t="n">
-        <v>198.9</v>
+        <v>198.45</v>
       </c>
       <c r="I50" t="n">
         <v>198.8768414878469</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.98</v>
+        <v>-3.2</v>
       </c>
       <c r="L50" t="n">
         <v>4.41</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.61</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44894</v>
+        <v>44895</v>
       </c>
       <c r="H51" t="n">
-        <v>193.65</v>
+        <v>194.5</v>
       </c>
       <c r="I51" t="n">
         <v>194.0898840512671</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K51" t="n">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="L51" t="n">
         <v>2.6</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.35</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H52" t="n">
-        <v>188.85</v>
+        <v>186.3</v>
       </c>
       <c r="I52" t="n">
         <v>187.9243776667532</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.9</v>
+        <v>-4.22</v>
       </c>
       <c r="L52" t="n">
         <v>4.68</v>
       </c>
       <c r="M52" t="n">
-        <v>0.58</v>
+        <v>0.95</v>
       </c>
       <c r="N52" t="n">
         <v>2.38</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.67</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H53" t="n">
-        <v>189.45</v>
+        <v>192.7</v>
       </c>
       <c r="I53" t="n">
         <v>190.9420031292895</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.69</v>
+        <v>-3.44</v>
       </c>
       <c r="L53" t="n">
-        <v>3.14</v>
+        <v>3.57</v>
       </c>
       <c r="M53" t="n">
         <v>1.04</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.35</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H54" t="n">
-        <v>187.95</v>
+        <v>186.6</v>
       </c>
       <c r="I54" t="n">
         <v>186.9968572180823</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.46</v>
+        <v>-3.17</v>
       </c>
       <c r="L54" t="n">
-        <v>2.62</v>
+        <v>4.41</v>
       </c>
       <c r="M54" t="n">
         <v>0.86</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.58</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45037</v>
+        <v>45040</v>
       </c>
       <c r="H55" t="n">
-        <v>175.85</v>
+        <v>180.65</v>
       </c>
       <c r="I55" t="n">
         <v>180.1414273083012</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K55" t="n">
-        <v>5.76</v>
+        <v>3.19</v>
       </c>
       <c r="L55" t="n">
         <v>1.58</v>
       </c>
       <c r="M55" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="N55" t="n">
-        <v>1.8</v>
+        <v>2.73</v>
       </c>
       <c r="O55" t="n">
         <v>-0.72</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.63</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45091</v>
+        <v>45092</v>
       </c>
       <c r="H56" t="n">
-        <v>189.45</v>
+        <v>185.9</v>
       </c>
       <c r="I56" t="n">
         <v>186.210993904592</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K56" t="n">
-        <v>4.87</v>
+        <v>2.91</v>
       </c>
       <c r="L56" t="n">
         <v>1.94</v>
@@ -3633,7 +4304,7 @@
         <v>0.79</v>
       </c>
       <c r="N56" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="O56" t="n">
         <v>2.73</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.43</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45120</v>
+        <v>45121</v>
       </c>
       <c r="H57" t="n">
-        <v>188.45</v>
+        <v>193.55</v>
       </c>
       <c r="I57" t="n">
         <v>189.4605700609625</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.37</v>
+        <v>-4.12</v>
       </c>
       <c r="L57" t="n">
-        <v>2.47</v>
+        <v>4.25</v>
       </c>
       <c r="M57" t="n">
         <v>1.21</v>
       </c>
       <c r="N57" t="n">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="O57" t="n">
         <v>-1.87</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.89</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45191</v>
+        <v>45194</v>
       </c>
       <c r="H58" t="n">
-        <v>200</v>
+        <v>197.9</v>
       </c>
       <c r="I58" t="n">
         <v>199.5038827986136</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K58" t="n">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
       <c r="L58" t="n">
         <v>3.1</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.33</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H59" t="n">
-        <v>187.15</v>
+        <v>189.8</v>
       </c>
       <c r="I59" t="n">
         <v>189.1752219474629</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K59" t="n">
-        <v>5.43</v>
+        <v>4.09</v>
       </c>
       <c r="L59" t="n">
         <v>2.37</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>5.29</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H60" t="n">
-        <v>239.15</v>
+        <v>232.8</v>
       </c>
       <c r="I60" t="n">
         <v>235.564019007468</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K60" t="n">
-        <v>26</v>
+        <v>22.66</v>
       </c>
       <c r="L60" t="n">
         <v>1.98</v>
       </c>
       <c r="M60" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="N60" t="n">
         <v>3.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.24</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="H61" t="n">
-        <v>220.3</v>
+        <v>231.6</v>
       </c>
       <c r="I61" t="n">
         <v>221.378181440372</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K61" t="n">
-        <v>5.37</v>
+        <v>0.52</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -3918,7 +4649,7 @@
         <v>2.72</v>
       </c>
       <c r="N61" t="n">
-        <v>3.03</v>
+        <v>5.13</v>
       </c>
       <c r="O61" t="n">
         <v>-2.66</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.27</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45492</v>
+        <v>45495</v>
       </c>
       <c r="H62" t="n">
-        <v>266.3</v>
+        <v>241.7</v>
       </c>
       <c r="I62" t="n">
         <v>251.5982534076048</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K62" t="n">
-        <v>14.98</v>
+        <v>4.36</v>
       </c>
       <c r="L62" t="n">
         <v>3.37</v>
       </c>
       <c r="M62" t="n">
-        <v>0.61</v>
+        <v>6.52</v>
       </c>
       <c r="N62" t="n">
-        <v>2.79</v>
+        <v>9.24</v>
       </c>
       <c r="O62" t="n">
         <v>5.13</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>12.56</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45531</v>
+        <v>45532</v>
       </c>
       <c r="H63" t="n">
-        <v>247.15</v>
+        <v>255.5</v>
       </c>
       <c r="I63" t="n">
         <v>252.0181977523072</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.25</v>
+        <v>-5.71</v>
       </c>
       <c r="L63" t="n">
-        <v>4.92</v>
+        <v>6.39</v>
       </c>
       <c r="M63" t="n">
         <v>1.88</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.07</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H64" t="n">
-        <v>284.4</v>
+        <v>279.4</v>
       </c>
       <c r="I64" t="n">
         <v>279.6383893351799</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K64" t="n">
-        <v>11.31</v>
+        <v>9.35</v>
       </c>
       <c r="L64" t="n">
         <v>4.01</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="H65" t="n">
-        <v>285.2</v>
+        <v>295.45</v>
       </c>
       <c r="I65" t="n">
         <v>293.8705455559535</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.08</v>
+        <v>-5.74</v>
       </c>
       <c r="L65" t="n">
-        <v>4.63</v>
+        <v>6.05</v>
       </c>
       <c r="M65" t="n">
         <v>7.11</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>10.6</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="H66" t="n">
-        <v>287.6</v>
+        <v>283.95</v>
       </c>
       <c r="I66" t="n">
         <v>286.2932539840793</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.66</v>
+        <v>-3.89</v>
       </c>
       <c r="L66" t="n">
-        <v>3.22</v>
+        <v>4.28</v>
       </c>
       <c r="M66" t="n">
         <v>1.1</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="H67" t="n">
-        <v>252.4</v>
+        <v>253.1</v>
       </c>
       <c r="I67" t="n">
         <v>252.8748188730412</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K67" t="n">
-        <v>11.11</v>
+        <v>10.86</v>
       </c>
       <c r="L67" t="n">
         <v>1.73</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>5.52</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H68" t="n">
-        <v>251.8</v>
+        <v>247.85</v>
       </c>
       <c r="I68" t="n">
         <v>249.1380902769524</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.51</v>
+        <v>-2.07</v>
       </c>
       <c r="L68" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="M68" t="n">
         <v>1.78</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.5</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="H69" t="n">
-        <v>247.75</v>
+        <v>250.45</v>
       </c>
       <c r="I69" t="n">
         <v>250.2101373822222</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K69" t="n">
-        <v>0.04</v>
+        <v>-1.05</v>
       </c>
       <c r="L69" t="n">
         <v>6.94</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>5.13</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H70" t="n">
-        <v>238.45</v>
+        <v>235.9</v>
       </c>
       <c r="I70" t="n">
         <v>237.6126352503439</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.79</v>
+        <v>-5.81</v>
       </c>
       <c r="L70" t="n">
-        <v>4.93</v>
+        <v>6.09</v>
       </c>
       <c r="M70" t="n">
         <v>2.87</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.55</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="H71" t="n">
-        <v>243.9</v>
+        <v>247.4</v>
       </c>
       <c r="I71" t="n">
         <v>246.931265709922</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.39</v>
+        <v>-4.87</v>
       </c>
       <c r="L71" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
         <v>0.65</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>6.17</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H72" t="n">
-        <v>234.45</v>
+        <v>231.95</v>
       </c>
       <c r="I72" t="n">
         <v>232.1293823204518</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.23</v>
+        <v>-6.24</v>
       </c>
       <c r="L72" t="n">
-        <v>5.78</v>
+        <v>6.41</v>
       </c>
       <c r="M72" t="n">
         <v>1.5</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>5.35</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="H73" t="n">
-        <v>239.45</v>
+        <v>243.9</v>
       </c>
       <c r="I73" t="n">
         <v>242.6008163747885</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.23</v>
+        <v>-5.15</v>
       </c>
       <c r="L73" t="n">
-        <v>4.81</v>
+        <v>5.3</v>
       </c>
       <c r="M73" t="n">
         <v>0.86</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.53</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="H74" t="n">
-        <v>260.7</v>
+        <v>239.75</v>
       </c>
       <c r="I74" t="n">
         <v>252.7285467890796</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K74" t="n">
-        <v>6.89</v>
+        <v>-1.7</v>
       </c>
       <c r="L74" t="n">
-        <v>1.82</v>
+        <v>3.46</v>
       </c>
       <c r="M74" t="n">
-        <v>0.47</v>
+        <v>5.77</v>
       </c>
       <c r="N74" t="n">
-        <v>3.18</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O74" t="n">
         <v>1.86</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>9.35</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H75" t="n">
-        <v>197.29</v>
+        <v>204.72</v>
       </c>
       <c r="I75" t="n">
         <v>203.9982483928576</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K75" t="n">
-        <v>17.71</v>
+        <v>14.61</v>
       </c>
       <c r="L75" t="n">
         <v>8.4</v>
@@ -4716,7 +5615,7 @@
         <v>6.98</v>
       </c>
       <c r="N75" t="n">
-        <v>2.07</v>
+        <v>3.77</v>
       </c>
       <c r="O75" t="n">
         <v>-8.039999999999999</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>10.11</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H76" t="n">
-        <v>196.68</v>
+        <v>189.57</v>
       </c>
       <c r="I76" t="n">
         <v>193.5670770710776</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.93</v>
+        <v>-7.4</v>
       </c>
       <c r="L76" t="n">
-        <v>4.19</v>
+        <v>7.63</v>
       </c>
       <c r="M76" t="n">
         <v>2.5</v>
       </c>
       <c r="N76" t="n">
-        <v>2.83</v>
+        <v>3.62</v>
       </c>
       <c r="O76" t="n">
         <v>3.77</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>8.01</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="H77" t="n">
-        <v>199.74</v>
+        <v>203.11</v>
       </c>
       <c r="I77" t="n">
         <v>200.4512151355892</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.36</v>
+        <v>-7.14</v>
       </c>
       <c r="L77" t="n">
-        <v>5.52</v>
+        <v>8.35</v>
       </c>
       <c r="M77" t="n">
         <v>0.85</v>
       </c>
       <c r="N77" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="O77" t="n">
         <v>-3.62</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>6.71</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H78" t="n">
-        <v>198.37</v>
+        <v>181.76</v>
       </c>
       <c r="I78" t="n">
         <v>193.7292747734194</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.33</v>
+        <v>-10.51</v>
       </c>
       <c r="L78" t="n">
-        <v>7.37</v>
+        <v>10.89</v>
       </c>
       <c r="M78" t="n">
         <v>6.26</v>
       </c>
       <c r="N78" t="n">
-        <v>2.91</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O78" t="n">
         <v>1.69</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>15.02</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="H79" t="n">
-        <v>183.61</v>
+        <v>186.33</v>
       </c>
       <c r="I79" t="n">
         <v>183.9238217591859</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.02</v>
+        <v>-2.51</v>
       </c>
       <c r="L79" t="n">
         <v>6.67</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>5.9</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H80" t="n">
-        <v>176.4</v>
+        <v>172.8</v>
       </c>
       <c r="I80" t="n">
         <v>175.5689051879261</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K80" t="n">
-        <v>-5.33</v>
+        <v>-7.26</v>
       </c>
       <c r="L80" t="n">
-        <v>5.69</v>
+        <v>7.34</v>
       </c>
       <c r="M80" t="n">
         <v>1.9</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>7.75</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H81" t="n">
-        <v>169</v>
+        <v>170.92</v>
       </c>
       <c r="I81" t="n">
         <v>170.2129246095792</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K81" t="n">
-        <v>2.2</v>
+        <v>1.09</v>
       </c>
       <c r="L81" t="n">
         <v>2.12</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5118,6 +6101,14 @@
       <c r="Q82" t="n">
         <v>10</v>
       </c>
+      <c r="R82" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10076,7 +11067,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.3</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="6">
@@ -10086,7 +11077,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -10096,7 +11087,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
@@ -10106,7 +11097,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -10116,7 +11107,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="10">
@@ -10126,7 +11117,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108.1</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="11">
@@ -10136,7 +11127,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -10146,7 +11137,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -10156,7 +11147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.2</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="14">
@@ -10166,7 +11157,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.97</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="15">
@@ -10176,7 +11167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.29</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="16">
@@ -10186,7 +11177,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.64</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="17">
@@ -10196,7 +11187,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>68.90000000000001</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -10206,7 +11197,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19">
@@ -10216,7 +11207,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.23</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="20">
@@ -10226,7 +11217,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.96</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="21">
@@ -10236,7 +11227,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -10246,7 +11237,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -10256,7 +11247,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -10266,7 +11257,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="25">
@@ -10286,7 +11277,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.08</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="27">
@@ -10306,7 +11297,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
